--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>118273464</v>
       </c>
       <c r="B2" t="n">
-        <v>97824</v>
+        <v>97831</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127048895</v>
       </c>
       <c r="B3" t="n">
-        <v>57654</v>
+        <v>57658</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127048895</v>
       </c>
       <c r="B3" t="n">
-        <v>57658</v>
+        <v>57660</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -785,7 +785,7 @@
         <v>127048895</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57654</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>118273464</v>
+        <v>127048895</v>
       </c>
       <c r="B2" t="n">
-        <v>97831</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,41 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219798</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lukaremyr (Lukaremyr), Gtl</t>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>720335</v>
+        <v>720303</v>
       </c>
       <c r="R2" t="n">
-        <v>6369117</v>
+        <v>6369093</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +745,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2025-07-14</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -763,33 +759,37 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>Tall med födosök av spillkråka.</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>127048895</v>
+        <v>127048896</v>
       </c>
       <c r="B3" t="n">
-        <v>57660</v>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>720303</v>
+        <v>720385</v>
       </c>
       <c r="R3" t="n">
-        <v>6369093</v>
+        <v>6369162</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -886,6 +886,645 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118273464</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lukaremyr, Lukaremyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>720335</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6369117</v>
+      </c>
+      <c r="S4" t="n">
+        <v>20</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>127048961</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>127048957</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>720377</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6369160</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>127048960</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>127048948</v>
+      </c>
+      <c r="B8" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>720257</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6369114</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog gles.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>127048946</v>
+      </c>
+      <c r="B9" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>720257</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6369114</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog gles.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -889,52 +889,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118273464</v>
+        <v>134659103</v>
       </c>
       <c r="B4" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lukaremyr, Lukaremyr, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>720335</v>
+        <v>720383</v>
       </c>
       <c r="R4" t="n">
-        <v>6369117</v>
+        <v>6369171</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -958,12 +954,27 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-07-07</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2 st förökningsyta</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -972,76 +983,66 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>127048961</v>
+        <v>134659105</v>
       </c>
       <c r="B5" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>720387</v>
+        <v>720368</v>
       </c>
       <c r="R5" t="n">
-        <v>6369164</v>
+        <v>6369154</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,12 +1066,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:09</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,78 +1092,64 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>127048957</v>
+        <v>134659107</v>
       </c>
       <c r="B6" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>720377</v>
+        <v>720371</v>
       </c>
       <c r="R6" t="n">
-        <v>6369160</v>
+        <v>6369183</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1176,12 +1173,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1192,78 +1199,64 @@
       </c>
       <c r="AG6" t="b">
         <v>0</v>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Anna Helmersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>127048960</v>
+        <v>134659355</v>
       </c>
       <c r="B7" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>720387</v>
+        <v>720389</v>
       </c>
       <c r="R7" t="n">
-        <v>6369164</v>
+        <v>6369181</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1287,12 +1280,27 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1303,31 +1311,26 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>127048948</v>
+        <v>134659357</v>
       </c>
       <c r="B8" t="n">
-        <v>104640</v>
+        <v>43472</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1335,37 +1338,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220164</v>
+        <v>101242</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>720257</v>
+        <v>720366</v>
       </c>
       <c r="R8" t="n">
-        <v>6369114</v>
+        <v>6369161</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1389,12 +1392,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:06</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1405,31 +1423,26 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog gles.</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Esmeralda Svanberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>127048946</v>
+        <v>134659361</v>
       </c>
       <c r="B9" t="n">
-        <v>107517</v>
+        <v>43472</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1437,37 +1450,37 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221849</v>
+        <v>101242</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Ala, Lauritse 1:38., Gtl</t>
+          <t>Ala Lauritse, Gtl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>720257</v>
+        <v>720349</v>
       </c>
       <c r="R9" t="n">
-        <v>6369114</v>
+        <v>6369140</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1491,12 +1504,27 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:25</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2025-07-14</t>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:25</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1507,24 +1535,770 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog gles.</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>134659362</v>
+      </c>
+      <c r="B10" t="n">
+        <v>43472</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Ala Lauritse, Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>720370</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6369166</v>
+      </c>
+      <c r="S10" t="n">
+        <v>5</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:27</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1st</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Esmeralda Svanberg</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118273464</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lukaremyr, Lukaremyr, Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>720335</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6369117</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-07</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>127048961</v>
+      </c>
+      <c r="B12" t="n">
+        <v>99096</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Jörgen Petersson</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>127048957</v>
+      </c>
+      <c r="B13" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>720377</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6369160</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>127048960</v>
+      </c>
+      <c r="B14" t="n">
+        <v>99142</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38. A 20833-2024, Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>720387</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6369164</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>127048948</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104640</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>720257</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6369114</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog gles.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>127048946</v>
+      </c>
+      <c r="B16" t="n">
+        <v>107517</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Ala, Lauritse 1:38., Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>720257</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6369114</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ala</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-07-14</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog gles.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -1315,12 +1315,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1427,12 +1427,12 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1539,12 +1539,12 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1651,12 +1651,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Esmeralda Svanberg</t>
+          <t>Esmeralda  Svanberg</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>

--- a/artfynd/A 20838-2024 artfynd.xlsx
+++ b/artfynd/A 20838-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AZ16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048895</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048896</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659103</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1105,6 +1125,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659105</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1212,6 +1237,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659107</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1324,6 +1354,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659355</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1436,6 +1471,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659357</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1548,6 +1588,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659361</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134659362</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1762,6 +1812,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118273464</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1873,6 +1928,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048961</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1984,6 +2044,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048957</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2095,6 +2160,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048960</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2197,6 +2267,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048948</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2299,8 +2374,30 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127048946</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>